--- a/docs/result/row-data/1st-test/pessimistic/pessimistic-lock-500-ngrinder-result.xlsx
+++ b/docs/result/row-data/1st-test/pessimistic/pessimistic-lock-500-ngrinder-result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sangja/Projects/concurrency-control-benchmarks/docs/result/row-data/1st-test/pessimistic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1913BA9-ECCD-E645-89E6-725754D96FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945176E8-EB77-6C40-A831-624AE5E67A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="660" windowWidth="14700" windowHeight="18460" xr2:uid="{735AB4FF-0B28-884A-8D84-5B4CF5579A12}"/>
   </bookViews>
@@ -4802,6 +4802,1470 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="738151" cy="355097"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="26" name="TextBox 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8E6BEF8-B9F4-E34B-8549-6EA3335C6BFF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="4114800"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="26" name="TextBox 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8E6BEF8-B9F4-E34B-8549-6EA3335C6BFF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="4114800"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(𝑛_𝑖−1) </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1599284" cy="182871"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27" name="TextBox 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C814E59-DBCB-664C-A318-2C8FC9262AC3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="5486400"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑤𝑖𝑡h𝑖𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27" name="TextBox 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C814E59-DBCB-664C-A318-2C8FC9262AC3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="5486400"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑤𝑖𝑡ℎ𝑖𝑛=Σ_(𝑖=1)^2 (𝑛_𝑖−1) 𝜎_𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="964816" cy="177228"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="TextBox 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8C81201-F659-4841-BF81-379F8D67281E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="5943600"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="TextBox 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8C81201-F659-4841-BF81-379F8D67281E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="5943600"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1984902" cy="186782"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="29" name="TextBox 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6405B156-AAAF-184E-9DF4-A915F50EEA63}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="7315200"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑏𝑒𝑡𝑤𝑒𝑒𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑘</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="29" name="TextBox 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6405B156-AAAF-184E-9DF4-A915F50EEA63}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="7315200"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑏𝑒𝑡𝑤𝑒𝑒𝑛=Σ_(𝑖=1)^𝑘 𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1842235" cy="500137"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="30" name="TextBox 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FFB4E39-846E-2647-AE32-FC0B9CBED9D4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="7772400"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>total</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:rad>
+                      <m:radPr>
+                        <m:degHide m:val="on"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:radPr>
+                      <m:deg/>
+                      <m:e>
+                        <m:f>
+                          <m:fPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:fPr>
+                          <m:num>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>within</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>between</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:num>
+                          <m:den>
+                            <m:r>
+                              <m:rPr>
+                                <m:sty m:val="p"/>
+                              </m:rPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>N</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−1</m:t>
+                            </m:r>
+                          </m:den>
+                        </m:f>
+                      </m:e>
+                    </m:rad>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="30" name="TextBox 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FFB4E39-846E-2647-AE32-FC0B9CBED9D4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="7772400"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>total=√((SS_within+SS_between)/(N-1))</a:t>
+              </a:r>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="438710" cy="173766"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="31" name="TextBox 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBC733A6-AD9B-6A42-B9D2-C5D6BABF622B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="8458200"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>2</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="31" name="TextBox 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBC733A6-AD9B-6A42-B9D2-C5D6BABF622B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4013200" y="8458200"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>2𝜎_𝑡𝑜𝑡𝑎𝑙</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5128,7 +6592,7 @@
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -5521,6 +6985,10 @@
         <f t="shared" ref="B19:B24" si="2">A12*B12</f>
         <v>11913.984</v>
       </c>
+      <c r="E19">
+        <f t="shared" ref="E19:E24" si="3">(A12-1)*POWER(C12,2)</f>
+        <v>788632.67167999991</v>
+      </c>
       <c r="H19" t="s">
         <v>13</v>
       </c>
@@ -5530,36 +6998,60 @@
         <f t="shared" si="2"/>
         <v>13386.99</v>
       </c>
+      <c r="E20">
+        <f t="shared" si="3"/>
+        <v>869982.06632400001</v>
+      </c>
     </row>
     <row r="21" spans="1:8">
       <c r="B21">
         <f t="shared" si="2"/>
         <v>169724.89799999999</v>
       </c>
+      <c r="E21">
+        <f t="shared" si="3"/>
+        <v>24879251.735028002</v>
+      </c>
     </row>
     <row r="22" spans="1:8">
       <c r="B22">
         <f t="shared" si="2"/>
         <v>65911.991999999998</v>
       </c>
+      <c r="E22">
+        <f t="shared" si="3"/>
+        <v>7125684.1507250005</v>
+      </c>
     </row>
     <row r="23" spans="1:8">
       <c r="B23">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
+      <c r="E23">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
       <c r="B24">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
+      <c r="E24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:8">
       <c r="B25">
         <f>SUM(B19:B24)</f>
         <v>260974.86399999997</v>
       </c>
+      <c r="E25">
+        <f>SUM(E19:E24)</f>
+        <v>33663550.873757005</v>
+      </c>
     </row>
     <row r="26" spans="1:8">
       <c r="B26">
@@ -5572,154 +7064,200 @@
         <f>B25/B26</f>
         <v>521.94972799999994</v>
       </c>
+      <c r="E27">
+        <f t="shared" ref="E27:E32" si="4">A12*POWER((B12-B$27),2)</f>
+        <v>15194997.435633596</v>
+      </c>
     </row>
     <row r="28" spans="1:8">
       <c r="B28">
         <f>ROUND(B27,2)</f>
         <v>521.95000000000005</v>
       </c>
+      <c r="E28">
+        <f t="shared" si="4"/>
+        <v>11290378.102120841</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="E29">
+        <f t="shared" si="4"/>
+        <v>15734620.957915148</v>
+      </c>
     </row>
     <row r="30" spans="1:8">
       <c r="B30">
-        <f t="shared" ref="B30:B35" si="3">POWER(C12,2)</f>
+        <f t="shared" ref="B30:B35" si="5">POWER(C12,2)</f>
         <v>8301.3965439999993</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="4"/>
+        <v>1574587.8828015965</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="B31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10356.929361</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="4"/>
+        <v>519078.05071854783</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="B32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>116803.99875600002</v>
       </c>
+      <c r="E32">
+        <f t="shared" si="4"/>
+        <v>260048.72508727392</v>
+      </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:5">
       <c r="B33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>70551.328225000005</v>
       </c>
+      <c r="E33">
+        <f>SUM(E27:E32)</f>
+        <v>44573711.154277012</v>
+      </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:5">
       <c r="B34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:5">
       <c r="B35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="E35">
+        <f>SQRT((E25+E33)/(B26-1))</f>
+        <v>395.96477148425868</v>
+      </c>
     </row>
-    <row r="36" spans="2:2">
+    <row r="36" spans="2:5">
       <c r="B36">
-        <f t="shared" ref="B36:B41" si="4">POWER(B12,2)</f>
+        <f t="shared" ref="B36:B41" si="6">POWER(B12,2)</f>
         <v>15401.802815999999</v>
       </c>
+      <c r="E36">
+        <f>ROUND(E35,2)</f>
+        <v>395.96</v>
+      </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:5">
       <c r="B37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>24804.360035999998</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:5">
       <c r="B38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>629018.71344899992</v>
       </c>
+      <c r="E38">
+        <f>2*E35</f>
+        <v>791.92954296851735</v>
+      </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:5">
       <c r="B39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>417569.27041600004</v>
       </c>
+      <c r="E39">
+        <f>ROUND(E38,2)</f>
+        <v>791.93</v>
+      </c>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="2:5">
       <c r="B40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>156.25</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:5">
       <c r="B41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>144</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:5">
       <c r="B42">
-        <f t="shared" ref="B42:B47" si="5">B30+B36</f>
+        <f t="shared" ref="B42:B47" si="7">B30+B36</f>
         <v>23703.199359999999</v>
       </c>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="2:5">
       <c r="B43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>35161.289397</v>
       </c>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="2:5">
       <c r="B44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>745822.71220499999</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:5">
       <c r="B45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>488120.59864100005</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="2:5">
       <c r="B46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>156.5</v>
       </c>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="2:5">
       <c r="B47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:5">
       <c r="B48">
-        <f t="shared" ref="B48:B53" si="6">A12*B42</f>
+        <f t="shared" ref="B48:B53" si="8">A12*B42</f>
         <v>2275507.1385599999</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2988709.5987450001</v>
       </c>
     </row>
     <row r="50" spans="2:6">
       <c r="B50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>159606060.41187</v>
       </c>
     </row>
     <row r="51" spans="2:6">
       <c r="B51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>49788301.061382003</v>
       </c>
     </row>
     <row r="52" spans="2:6">
       <c r="B52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>313</v>
       </c>
     </row>
     <row r="53" spans="2:6">
       <c r="B53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>144</v>
       </c>
     </row>
